--- a/Veenkampen/misc/BADM-Instrument/VK-BADM-Instrument-v2020.xlsx
+++ b/Veenkampen/misc/BADM-Instrument/VK-BADM-Instrument-v2020.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\ESG\DOW_MAQ\MAQ_Archive\Veenkampen_archive\FLUXNET\Veenkampen\misc\BADM-Instrument\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15F207-ADA1-4D96-BC85-721FB5610B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99050BB6-2DF9-4997-8E2C-EB3AAFBA0DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54495" yWindow="-6525" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrument" sheetId="1" r:id="rId1"/>
@@ -1983,18 +1983,17 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
